--- a/dataCrim.xlsx
+++ b/dataCrim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JoseManuel/Documents/GITHUBs/PUCP/PostGrado/Gob_TomaDeDecisiones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{773D3771-5E5C-7549-9FC9-8F504A0FA159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD704F5A-45CE-3047-8C58-512FB8D81D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="16440" xr2:uid="{ABF07EC7-6226-A94A-AA78-C00FAF67B8E1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7440" uniqueCount="3565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7442" uniqueCount="3567">
   <si>
     <t>010101</t>
   </si>
@@ -10728,6 +10728,12 @@
   </si>
   <si>
     <t>PURUS</t>
+  </si>
+  <si>
+    <t>cod</t>
+  </si>
+  <si>
+    <t>distrito</t>
   </si>
 </sst>
 </file>
@@ -11611,6 +11617,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>3565</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3566</v>
+      </c>
       <c r="C1" s="1">
         <v>2015</v>
       </c>

--- a/dataCrim.xlsx
+++ b/dataCrim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JoseManuel/Documents/GITHUBs/PUCP/PostGrado/Gob_TomaDeDecisiones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9F61DF-8C0C-B14B-BA14-DB24845AF56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390A5B9C-0D5E-8249-A85E-96D06DE36809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="16440" xr2:uid="{768E452D-7CBB-194B-9A0B-E7A6B6C5CD37}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6726" uniqueCount="4462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6727" uniqueCount="4462">
   <si>
     <t>AMAZONAS</t>
   </si>
@@ -13403,9 +13403,6 @@
     <t>250305</t>
   </si>
   <si>
-    <t>250401</t>
-  </si>
-  <si>
     <t>cod</t>
   </si>
   <si>
@@ -13419,6 +13416,9 @@
   </si>
   <si>
     <t>LIMA METROPOLITANA</t>
+  </si>
+  <si>
+    <t>ALEXANDER VON HUMBOLDT</t>
   </si>
 </sst>
 </file>
@@ -14439,16 +14439,16 @@
   <sheetData>
     <row r="1" spans="1:20" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>4460</v>
+        <v>4459</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>4456</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>4457</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4458</v>
       </c>
       <c r="E1" s="5">
         <v>2015</v>
@@ -77233,7 +77233,7 @@
     </row>
     <row r="1390" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1390" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1390" s="5" t="s">
         <v>523</v>
@@ -77283,7 +77283,7 @@
     </row>
     <row r="1391" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1391" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1391" s="10"/>
       <c r="C1391" s="8" t="s">
@@ -77331,7 +77331,7 @@
     </row>
     <row r="1392" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1392" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1392" s="10"/>
       <c r="C1392" s="8" t="s">
@@ -77379,7 +77379,7 @@
     </row>
     <row r="1393" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1393" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1393" s="10"/>
       <c r="C1393" s="8" t="s">
@@ -77427,7 +77427,7 @@
     </row>
     <row r="1394" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1394" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1394" s="10"/>
       <c r="C1394" s="8" t="s">
@@ -77475,7 +77475,7 @@
     </row>
     <row r="1395" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1395" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1395" s="10"/>
       <c r="C1395" s="8" t="s">
@@ -77523,7 +77523,7 @@
     </row>
     <row r="1396" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1396" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1396" s="10"/>
       <c r="C1396" s="8" t="s">
@@ -77571,7 +77571,7 @@
     </row>
     <row r="1397" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1397" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1397" s="10"/>
       <c r="C1397" s="8" t="s">
@@ -77619,7 +77619,7 @@
     </row>
     <row r="1398" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1398" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1398" s="10"/>
       <c r="C1398" s="8" t="s">
@@ -77667,7 +77667,7 @@
     </row>
     <row r="1399" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1399" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1399" s="10"/>
       <c r="C1399" s="8" t="s">
@@ -77715,7 +77715,7 @@
     </row>
     <row r="1400" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1400" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1400" s="10"/>
       <c r="C1400" s="8" t="s">
@@ -77763,7 +77763,7 @@
     </row>
     <row r="1401" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1401" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1401" s="10"/>
       <c r="C1401" s="8" t="s">
@@ -77811,7 +77811,7 @@
     </row>
     <row r="1402" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1402" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1402" s="10"/>
       <c r="C1402" s="8" t="s">
@@ -77859,7 +77859,7 @@
     </row>
     <row r="1403" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1403" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1403" s="10"/>
       <c r="C1403" s="8" t="s">
@@ -77907,7 +77907,7 @@
     </row>
     <row r="1404" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1404" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1404" s="10"/>
       <c r="C1404" s="8" t="s">
@@ -77955,7 +77955,7 @@
     </row>
     <row r="1405" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1405" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1405" s="10"/>
       <c r="C1405" s="8" t="s">
@@ -78003,7 +78003,7 @@
     </row>
     <row r="1406" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1406" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1406" s="10"/>
       <c r="C1406" s="8" t="s">
@@ -78051,7 +78051,7 @@
     </row>
     <row r="1407" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1407" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1407" s="10"/>
       <c r="C1407" s="8" t="s">
@@ -78099,7 +78099,7 @@
     </row>
     <row r="1408" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1408" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1408" s="10"/>
       <c r="C1408" s="8" t="s">
@@ -78147,7 +78147,7 @@
     </row>
     <row r="1409" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1409" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1409" s="10"/>
       <c r="C1409" s="8" t="s">
@@ -78195,7 +78195,7 @@
     </row>
     <row r="1410" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1410" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1410" s="10"/>
       <c r="C1410" s="8" t="s">
@@ -78243,7 +78243,7 @@
     </row>
     <row r="1411" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1411" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1411" s="10"/>
       <c r="C1411" s="8" t="s">
@@ -78291,7 +78291,7 @@
     </row>
     <row r="1412" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1412" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1412" s="10"/>
       <c r="C1412" s="8" t="s">
@@ -78339,7 +78339,7 @@
     </row>
     <row r="1413" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1413" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1413" s="10"/>
       <c r="C1413" s="8" t="s">
@@ -78387,7 +78387,7 @@
     </row>
     <row r="1414" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1414" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1414" s="10"/>
       <c r="C1414" s="8" t="s">
@@ -78435,7 +78435,7 @@
     </row>
     <row r="1415" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1415" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1415" s="10"/>
       <c r="C1415" s="8" t="s">
@@ -78483,7 +78483,7 @@
     </row>
     <row r="1416" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1416" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1416" s="10"/>
       <c r="C1416" s="8" t="s">
@@ -78531,7 +78531,7 @@
     </row>
     <row r="1417" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1417" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1417" s="10"/>
       <c r="C1417" s="8" t="s">
@@ -78579,7 +78579,7 @@
     </row>
     <row r="1418" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1418" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1418" s="10"/>
       <c r="C1418" s="8" t="s">
@@ -78627,7 +78627,7 @@
     </row>
     <row r="1419" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1419" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1419" s="10"/>
       <c r="C1419" s="8" t="s">
@@ -78675,7 +78675,7 @@
     </row>
     <row r="1420" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1420" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1420" s="10"/>
       <c r="C1420" s="8" t="s">
@@ -78723,7 +78723,7 @@
     </row>
     <row r="1421" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1421" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1421" s="10"/>
       <c r="C1421" s="8" t="s">
@@ -78771,7 +78771,7 @@
     </row>
     <row r="1422" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1422" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1422" s="10"/>
       <c r="C1422" s="8" t="s">
@@ -78819,7 +78819,7 @@
     </row>
     <row r="1423" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1423" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1423" s="10"/>
       <c r="C1423" s="8" t="s">
@@ -78867,7 +78867,7 @@
     </row>
     <row r="1424" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1424" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1424" s="10"/>
       <c r="C1424" s="8" t="s">
@@ -78915,7 +78915,7 @@
     </row>
     <row r="1425" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1425" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1425" s="10"/>
       <c r="C1425" s="8" t="s">
@@ -78963,7 +78963,7 @@
     </row>
     <row r="1426" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1426" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1426" s="10"/>
       <c r="C1426" s="8" t="s">
@@ -79011,7 +79011,7 @@
     </row>
     <row r="1427" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1427" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1427" s="10"/>
       <c r="C1427" s="8" t="s">
@@ -79059,7 +79059,7 @@
     </row>
     <row r="1428" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1428" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1428" s="10"/>
       <c r="C1428" s="8" t="s">
@@ -79107,7 +79107,7 @@
     </row>
     <row r="1429" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1429" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1429" s="10"/>
       <c r="C1429" s="8" t="s">
@@ -79155,7 +79155,7 @@
     </row>
     <row r="1430" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1430" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1430" s="10"/>
       <c r="C1430" s="8" t="s">
@@ -79203,7 +79203,7 @@
     </row>
     <row r="1431" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1431" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1431" s="10"/>
       <c r="C1431" s="8" t="s">
@@ -79251,7 +79251,7 @@
     </row>
     <row r="1432" spans="1:20" ht="19" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1432" s="5" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
       <c r="B1432" s="11"/>
       <c r="C1432" s="9" t="s">
@@ -98765,8 +98765,8 @@
       <c r="C1858" s="9" t="s">
         <v>4455</v>
       </c>
-      <c r="D1858" s="1" t="e">
-        <v>#N/A</v>
+      <c r="D1858" t="s">
+        <v>4461</v>
       </c>
       <c r="E1858" s="3"/>
       <c r="F1858" s="3"/>
@@ -98808,11 +98808,11 @@
       <c r="B1859" s="2" t="s">
         <v>1037</v>
       </c>
-      <c r="C1859" s="1" t="s">
-        <v>4456</v>
-      </c>
-      <c r="D1859" s="1" t="e">
-        <v>#N/A</v>
+      <c r="C1859" s="1">
+        <v>250401</v>
+      </c>
+      <c r="D1859" s="2" t="s">
+        <v>1037</v>
       </c>
       <c r="E1859" s="4">
         <v>37</v>
